--- a/Excel/CardTable.xlsx
+++ b/Excel/CardTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Crockhead.Unity.Workbench\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MillenniumOfCultivation\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14610B45-3EF9-4C3B-8C3E-16252C0295DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028EEDEE-4299-4330-9A2E-1942C23999EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="43">
   <si>
     <t>FIELD</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,13 +50,151 @@
     <t>string</t>
   </si>
   <si>
-    <t>브로드 소드 A</t>
-  </si>
-  <si>
-    <t>배틀 액스 B</t>
-  </si>
-  <si>
     <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고유 식별자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소모 행동력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카드 종류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardActionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardTargetType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용 종류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용시 적용 대상 종류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionTarget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CostAP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionSkillTableId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용시 발동되는 스킬의 스킬 테이블 고유 식별자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GradeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등급 종류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mythic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uncommon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>풍신퇴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호체공</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격+1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -80,7 +218,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -88,8 +227,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -126,40 +264,47 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,19 +586,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.08203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -461,173 +610,389 @@
         <v>4</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>10000001</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="6">
+        <v>10000001</v>
+      </c>
+      <c r="I5" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="6" t="s">
+      <c r="J5" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7">
-        <v>10000001</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="6" t="s">
+      <c r="B6" s="6">
+        <v>10000002</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="6">
+        <v>10000002</v>
+      </c>
+      <c r="I6" s="6">
+        <v>1</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="7">
-        <v>10000001</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="6" t="s">
+      <c r="B7" s="6">
+        <v>10000003</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="6">
+        <v>10000003</v>
+      </c>
+      <c r="I7" s="6">
+        <v>1</v>
+      </c>
+      <c r="J7" s="7"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="7">
-        <v>10000001</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="6" t="s">
+      <c r="B8" s="6">
+        <v>10000004</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="6">
+        <v>10000004</v>
+      </c>
+      <c r="I8" s="6">
+        <v>1</v>
+      </c>
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="7">
-        <v>10000001</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="6" t="s">
+      <c r="B9" s="6">
+        <v>10000005</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="6">
+        <v>10000005</v>
+      </c>
+      <c r="I9" s="6">
+        <v>1</v>
+      </c>
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="7">
-        <v>10000001</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="6" t="s">
+      <c r="B10" s="6">
+        <v>10000006</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="6">
+        <v>10000006</v>
+      </c>
+      <c r="I10" s="6"/>
+      <c r="J10" s="7"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="7">
-        <v>10000001</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" s="6" t="s">
+      <c r="B11" s="6">
+        <v>10000007</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="6">
+        <v>10000007</v>
+      </c>
+      <c r="I11" s="6">
         <v>2</v>
       </c>
-      <c r="B10" s="7">
-        <v>10000001</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" s="6" t="s">
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="7">
-        <v>10000001</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" s="6" t="s">
+      <c r="B12" s="6">
+        <v>10000008</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="6">
+        <v>10000008</v>
+      </c>
+      <c r="I12" s="6"/>
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="7">
-        <v>10000001</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" s="6" t="s">
+      <c r="B13" s="6">
+        <v>10000009</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="6">
+        <v>10000009</v>
+      </c>
+      <c r="I13" s="6"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="7">
-        <v>10000001</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13"/>
+      <c r="B14" s="6">
+        <v>10000010</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="6">
+        <v>10000010</v>
+      </c>
+      <c r="I14" s="6"/>
+      <c r="J14" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Excel/CardTable.xlsx
+++ b/Excel/CardTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MillenniumOfCultivation\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028EEDEE-4299-4330-9A2E-1942C23999EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84447B9F-B723-4B42-8F16-E093DC9BDDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="#CardTable" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="67">
   <si>
     <t>FIELD</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,7 +194,103 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공격+1</t>
+    <t>정혈 태우기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지정한 대상에게 공격력+1의 피해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용시 최대 체력의 30% 소모, 다음 행동의 효과 2배</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소지시 신식+1, 법력+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무명원신비법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AssetPath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shops</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>번천인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>U</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주작선: 염열파</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주작의 불꽃을 사방으로 방출한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적용 대상이 집단인가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>All</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>괴뢰 소환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>은신술</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>은신: 1턴간 대상 지정 회피</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백호 소환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀호 소환</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -586,23 +682,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.08203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.4140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.6640625" style="1"/>
+    <col min="8" max="8" width="18.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="40.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.08203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="42.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -625,16 +725,28 @@
         <v>23</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
@@ -657,16 +769,24 @@
         <v>20</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="4"/>
+      <c r="K2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M2" s="4"/>
+      <c r="N2" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
@@ -689,16 +809,24 @@
         <v>22</v>
       </c>
       <c r="H3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M3" s="4"/>
+      <c r="N3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -711,8 +839,12 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
@@ -732,19 +864,23 @@
         <v>38</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="6">
+        <v>45</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6">
         <v>10000001</v>
       </c>
-      <c r="I5" s="6">
+      <c r="J5" s="6"/>
+      <c r="K5" s="6">
         <v>1</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
@@ -766,24 +902,30 @@
       <c r="G6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="6"/>
+      <c r="I6" s="6">
         <v>10000002</v>
       </c>
-      <c r="I6" s="6">
+      <c r="J6" s="6"/>
+      <c r="K6" s="6">
         <v>1</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="6">
         <v>10000003</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="6" t="s">
+        <v>63</v>
+      </c>
       <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
@@ -796,15 +938,21 @@
       <c r="G7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="6"/>
+      <c r="I7" s="6">
         <v>10000003</v>
       </c>
-      <c r="I7" s="6">
+      <c r="J7" s="6"/>
+      <c r="K7" s="6">
         <v>1</v>
       </c>
-      <c r="J7" s="7"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
         <v>2</v>
       </c>
@@ -824,15 +972,19 @@
       <c r="G8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="6"/>
+      <c r="I8" s="6">
         <v>10000004</v>
       </c>
-      <c r="I8" s="6">
+      <c r="J8" s="6"/>
+      <c r="K8" s="6">
         <v>1</v>
       </c>
-      <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="7"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
         <v>2</v>
       </c>
@@ -852,15 +1004,19 @@
       <c r="G9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="6"/>
+      <c r="I9" s="6">
         <v>10000005</v>
       </c>
-      <c r="I9" s="6">
+      <c r="J9" s="6"/>
+      <c r="K9" s="6">
         <v>1</v>
       </c>
-      <c r="J9" s="7"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="7"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
         <v>2</v>
       </c>
@@ -880,13 +1036,17 @@
       <c r="G10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="6"/>
+      <c r="I10" s="6">
         <v>10000006</v>
       </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
         <v>2</v>
       </c>
@@ -908,15 +1068,19 @@
       <c r="G11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="6"/>
+      <c r="I11" s="6">
         <v>10000007</v>
       </c>
-      <c r="I11" s="6">
-        <v>2</v>
-      </c>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J11" s="6"/>
+      <c r="K11" s="6">
+        <v>2</v>
+      </c>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
         <v>2</v>
       </c>
@@ -936,13 +1100,17 @@
       <c r="G12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="6"/>
+      <c r="I12" s="6">
         <v>10000008</v>
       </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="7"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
         <v>2</v>
       </c>
@@ -962,13 +1130,17 @@
       <c r="G13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="6"/>
+      <c r="I13" s="6">
         <v>10000009</v>
       </c>
-      <c r="I13" s="6"/>
-      <c r="J13" s="7"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="7"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
         <v>2</v>
       </c>
@@ -988,11 +1160,795 @@
       <c r="G14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="6"/>
+      <c r="I14" s="6">
         <v>10000010</v>
       </c>
-      <c r="I14" s="6"/>
-      <c r="J14" s="7"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="7"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="7"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A16" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="6">
+        <v>10000011</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6">
+        <v>10000011</v>
+      </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6">
+        <v>0</v>
+      </c>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6">
+        <v>0</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="6">
+        <v>10000012</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6">
+        <v>10000012</v>
+      </c>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6">
+        <v>0</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A18" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="6">
+        <v>10000013</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" s="6">
+        <v>10000013</v>
+      </c>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="7"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A19" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="6">
+        <v>10000014</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" s="6">
+        <v>10000014</v>
+      </c>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M19" s="6"/>
+      <c r="N19" s="7"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A20" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="6">
+        <v>10000015</v>
+      </c>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6">
+        <v>10000015</v>
+      </c>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="7"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A21" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="6">
+        <v>10000016</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6">
+        <v>10000016</v>
+      </c>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="7"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="6">
+        <v>10000017</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6">
+        <v>10000017</v>
+      </c>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="7"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10000018</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6">
+        <v>10000018</v>
+      </c>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="7"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="6">
+        <v>10000019</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6">
+        <v>10000019</v>
+      </c>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="7"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A25" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="6">
+        <v>10000020</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6">
+        <v>10000020</v>
+      </c>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="7"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A26" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" s="6">
+        <v>10000021</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6">
+        <v>10000021</v>
+      </c>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="7"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A27" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="6">
+        <v>10000022</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6">
+        <v>10000022</v>
+      </c>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="7"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A28" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="6">
+        <v>10000023</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6">
+        <v>10000023</v>
+      </c>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="7"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A29" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="6">
+        <v>10000024</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6">
+        <v>10000024</v>
+      </c>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="7"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A30" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" s="6">
+        <v>10000025</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6">
+        <v>10000025</v>
+      </c>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="7"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A31" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" s="6">
+        <v>10000026</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6">
+        <v>10000026</v>
+      </c>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="7"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" s="6">
+        <v>10000027</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6">
+        <v>10000027</v>
+      </c>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="7"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" s="6">
+        <v>10000028</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6">
+        <v>10000028</v>
+      </c>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="7"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" s="6">
+        <v>10000029</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6">
+        <v>10000029</v>
+      </c>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="7"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B35" s="6">
+        <v>10000030</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6">
+        <v>10000030</v>
+      </c>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="7"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" s="6">
+        <v>10000031</v>
+      </c>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6">
+        <v>10000031</v>
+      </c>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="7"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="6">
+        <v>10000032</v>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6">
+        <v>10000032</v>
+      </c>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="7"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B38" s="6">
+        <v>10000033</v>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6">
+        <v>10000033</v>
+      </c>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="7"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="6">
+        <v>10000034</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6">
+        <v>10000034</v>
+      </c>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="7"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" s="6">
+        <v>10000035</v>
+      </c>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6">
+        <v>10000035</v>
+      </c>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="7"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B41" s="6">
+        <v>10000036</v>
+      </c>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6">
+        <v>10000036</v>
+      </c>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Excel/CardTable.xlsx
+++ b/Excel/CardTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MillenniumOfCultivation\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84447B9F-B723-4B42-8F16-E093DC9BDDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350E4593-823F-436A-B83F-EE7B3C5BCDBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="65">
   <si>
     <t>FIELD</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,19 +106,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CardTargetType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>사용 종류</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>사용시 적용 대상 종류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionTarget</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -716,31 +708,27 @@
         <v>9</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
       <c r="I1" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>12</v>
@@ -760,17 +748,13 @@
         <v>9</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
         <v>3</v>
       </c>
@@ -800,19 +784,19 @@
         <v>17</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4" t="s">
@@ -852,19 +836,19 @@
         <v>10000001</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6">
@@ -877,7 +861,7 @@
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.45">
@@ -888,16 +872,16 @@
         <v>10000002</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>16</v>
@@ -913,7 +897,7 @@
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.45">
@@ -924,13 +908,13 @@
         <v>10000003</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>16</v>
@@ -949,7 +933,7 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.45">
@@ -964,7 +948,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>16</v>
@@ -996,7 +980,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>16</v>
@@ -1028,7 +1012,7 @@
         <v>16</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>16</v>
@@ -1054,13 +1038,13 @@
         <v>10000007</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>16</v>
@@ -1092,7 +1076,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>16</v>
@@ -1122,7 +1106,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>16</v>
@@ -1152,7 +1136,7 @@
         <v>16</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>16</v>
@@ -1194,19 +1178,19 @@
         <v>10000011</v>
       </c>
       <c r="C16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6">
@@ -1221,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.45">
@@ -1232,19 +1216,19 @@
         <v>10000012</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6">
@@ -1257,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.45">
@@ -1268,22 +1252,22 @@
         <v>10000013</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I18" s="6">
         <v>10000013</v>
@@ -1302,7 +1286,7 @@
         <v>10000014</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>16</v>
@@ -1312,10 +1296,10 @@
         <v>16</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I19" s="6">
         <v>10000014</v>
@@ -1323,7 +1307,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M19" s="6"/>
       <c r="N19" s="7"/>
@@ -1364,7 +1348,7 @@
         <v>10000016</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>16</v>
@@ -1394,7 +1378,7 @@
         <v>10000017</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>16</v>
@@ -1424,7 +1408,7 @@
         <v>10000018</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>16</v>
